--- a/argus/kship/models/092460_model.xlsx
+++ b/argus/kship/models/092460_model.xlsx
@@ -4724,7 +4724,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 9.6, "op_wape_pct": 13.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 321.98, "rev_act": 316.68, "op_pred": 49.37, "op_act": 54.41}, {"q": "2025Q4", "rev_pred": 446.31, "rev_act": 395.91, "op_pred": 68.43, "op_act": 55.42}, {"q": "2026Q1", "rev_pred": 367.28, "rev_act": 393.57, "op_pred": 56.32, "op_act": 55.18}, {"q": "2026Q2", "rev_pred": 493.23, "rev_act": 428.36, "op_pred": 75.63, "op_act": 91.94}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 9.6, "op_wape_pct": 13.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 321.98, "rev_act": 316.68, "op_pred": 49.37, "op_act": 54.41}, {"q": "2025Q4", "rev_pred": 446.31, "rev_act": 395.91, "op_pred": 68.43, "op_act": 55.42}, {"q": "2026Q1", "rev_pred": 367.28, "rev_act": 393.57, "op_pred": 56.32, "op_act": 55.18}, {"q": "2026Q2", "rev_pred": 493.23, "rev_act": 428.36, "op_pred": 75.63, "op_act": 91.94}]}</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19049,7 +19049,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/092460_model.xlsx
+++ b/argus/kship/models/092460_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 169959억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 169925억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 178831억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 178760억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 165091억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 164983억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164564억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 164420억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 163090억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 162942억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 169959억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 169925억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 178831억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 178760억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 165091억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 164983억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164564억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 164420억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 163090억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 162942억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4179,7 +4179,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5050,35 +5050,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5169,35 +5169,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5288,35 +5288,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5407,35 +5407,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5526,35 +5526,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5645,35 +5645,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5764,35 +5764,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5883,35 +5883,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6018,7 +6018,7 @@
         <v>16830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>16830</v>
+        <v>16950</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6109,7 +6109,7 @@
         <v>19040</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>16940</v>
+        <v>17180</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6291,7 +6291,7 @@
         <v>16620.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>16835</v>
+        <v>16873.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6459,20 +6459,20 @@
         <v>0.266889052</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.329539565</v>
+        <v>0.329258811</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.391648237</v>
+        <v>0.391075842</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.100655212</v>
+        <v>0.099924945</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.021685148</v>
+        <v>0.02078606</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.040430128</v>
+        <v>-0.041088546</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6773,23 +6773,23 @@
         <v>0.161750225</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.161753001</v>
+        <v>0.161754671</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.161755908</v>
+        <v>0.161747653</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.161742752</v>
+        <v>0.161757926</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.161753305</v>
+        <v>0.161748978</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.161746284</v>
+        <v>0.161755985</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7814,36 +7814,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.003261161</v>
+        <v>-0.003158196</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-1.7482e-05</v>
+        <v>0.000202523</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.003014873</v>
+        <v>-0.002851566</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>106.075386107</v>
+        <v>106.075665845</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.005311471</v>
+        <v>-0.00456695</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.00029873</v>
+        <v>0.004084049</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.004945311</v>
+        <v>-0.008533199999999999</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>106.0793387</v>
+        <v>106.076929077</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.008016268</v>
+        <v>0.002512227</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.009107956</v>
+        <v>-0.007459869</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7942,36 +7942,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.003261161</v>
+        <v>-0.003158196</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-1.7482e-05</v>
+        <v>0.000202523</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.003014873</v>
+        <v>-0.002851566</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>106.075386107</v>
+        <v>106.075665845</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.005311471</v>
+        <v>-0.00456695</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.00029873</v>
+        <v>0.004084049</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.004945311</v>
+        <v>-0.008533199999999999</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>106.0793387</v>
+        <v>106.076929077</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.008016268</v>
+        <v>0.002512227</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.009107956</v>
+        <v>-0.007459869</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8214,20 +8214,20 @@
         <v>-0.001963351</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.049953162</v>
+        <v>-0.049906323</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.025562649</v>
+        <v>-0.025487441</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.239210726</v>
+        <v>0.239306943</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.003511207</v>
+        <v>-0.003408442</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.03560454</v>
+        <v>-0.035450245</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8342,20 +8342,20 @@
         <v>0.005366839</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.133957169</v>
+        <v>0.133831564</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.057432432</v>
+        <v>0.057272627</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.495260043</v>
+        <v>-0.495651718</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.017847878</v>
+        <v>0.017347045</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.177184219</v>
+        <v>0.176740862</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>16830</v>
+        <v>16950</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.147440882146727</v>
+        <v>0.1474368783473604</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1604224136883423</v>
+        <v>0.1604216642894191</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03941208534844564</v>
+        <v>0.03938949465628151</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02198785830668719</v>
+        <v>0.02197790204990261</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32813,7 +32813,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40086,7 +40086,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.34</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="32">
@@ -40096,7 +40096,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="33">
@@ -40136,7 +40136,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.77</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/092460_model.xlsx
+++ b/argus/kship/models/092460_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 169925억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 169896억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 178760억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 178685억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164983억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 164865억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164420억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 164256억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 162942억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 162764억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 169925억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 169896억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 178760억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 178685억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164983억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 164865억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164420억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 164256억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 162942억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 162764억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4179,7 +4179,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5050,35 +5050,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5169,35 +5169,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5288,35 +5288,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5407,35 +5407,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5526,35 +5526,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5645,35 +5645,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5764,35 +5764,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5883,35 +5883,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6018,7 +6018,7 @@
         <v>16830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>16950</v>
+        <v>17080</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6200,7 +6200,7 @@
         <v>13770</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>16570</v>
+        <v>16000</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6291,7 +6291,7 @@
         <v>16620.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>16873.3</v>
+        <v>16935</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6459,20 +6459,20 @@
         <v>0.266889052</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.329258811</v>
+        <v>0.329042847</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.391075842</v>
+        <v>0.390503447</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.099924945</v>
+        <v>0.099133822</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.02078606</v>
+        <v>0.019779937</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.041088546</v>
+        <v>-0.04198895</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6773,23 +6773,23 @@
         <v>0.161750225</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.161754671</v>
+        <v>0.161748456</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.161747653</v>
+        <v>0.161758102</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.161757926</v>
+        <v>0.161745165</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.161748978</v>
+        <v>0.161740627</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.161755985</v>
+        <v>0.161747744</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7814,36 +7814,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.003158196</v>
+        <v>-0.003742252</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.000202523</v>
+        <v>-0.000433648</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.002851566</v>
+        <v>-0.003401123</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>106.075665845</v>
+        <v>106.07503697</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.00456695</v>
+        <v>-0.004657985</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.004084049</v>
+        <v>-0.003237208</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.008533199999999999</v>
+        <v>0.005524083</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>106.076929077</v>
+        <v>106.066571534</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.002512227</v>
+        <v>-0.006237553</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.007459869</v>
+        <v>-0.002599105</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7942,36 +7942,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.003158196</v>
+        <v>-0.003742252</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.000202523</v>
+        <v>-0.000433648</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.002851566</v>
+        <v>-0.003401123</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>106.075665845</v>
+        <v>106.07503697</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.00456695</v>
+        <v>-0.004657985</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.004084049</v>
+        <v>-0.003237208</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.008533199999999999</v>
+        <v>0.005524083</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>106.076929077</v>
+        <v>106.066571534</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.002512227</v>
+        <v>-0.006237553</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.007459869</v>
+        <v>-0.002599105</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8214,20 +8214,20 @@
         <v>-0.001963351</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.049906323</v>
+        <v>-0.049882904</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.025487441</v>
+        <v>-0.025412867</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.239306943</v>
+        <v>0.239409191</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.003408442</v>
+        <v>-0.003244567</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.035450245</v>
+        <v>-0.035253654</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8342,20 +8342,20 @@
         <v>0.005366839</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.133831564</v>
+        <v>0.133768762</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.057272627</v>
+        <v>0.057109622</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.495651718</v>
+        <v>-0.496017606</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.017347045</v>
+        <v>0.016531503</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.176740862</v>
+        <v>0.176127647</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9018,11 +9018,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>16950</v>
+        <v>17080</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,790원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,830원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1474368783473604</v>
+        <v>0.1474441567056602</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1604216642894191</v>
+        <v>0.1604203613810716</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03938949465628151</v>
+        <v>0.03936622001636177</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02197790204990261</v>
+        <v>0.0219677827402049</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32813,7 +32813,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40086,7 +40086,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.43</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="32">
@@ -40096,7 +40096,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="33">
@@ -40136,7 +40136,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.84</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/092460_model.xlsx
+++ b/argus/kship/models/092460_model.xlsx
@@ -681,37 +681,37 @@
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 161069억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 160141억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 169896억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167314억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 178685억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 175973억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164865억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 164233억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164256억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 169448억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 162764억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 177774억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1668,37 +1668,37 @@
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 161069억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 160141억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 169896억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167314억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 178685억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 175973억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164865억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 164233억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164256억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 169448억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 162764억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 177774억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2040,25 +2040,25 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 181억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 179억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 191억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 188억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 96억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 93억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 98억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 97억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2100,25 +2100,25 @@
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 181억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 179억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 191억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 188억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 96억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 93억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 98억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 97억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4179,7 +4179,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -6456,23 +6456,23 @@
         <v>0.150825435</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.266889052</v>
+        <v>0.259566621</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.329042847</v>
+        <v>0.308850207</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.390503447</v>
+        <v>0.369402888</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.099133822</v>
+        <v>0.09493478299999999</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.019779937</v>
+        <v>0.058134528</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.04198895</v>
+        <v>0.062503094</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6770,26 +6770,26 @@
         <v>0.161754265</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.161750225</v>
+        <v>0.161743175</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.161748456</v>
+        <v>0.161752331</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.161758102</v>
+        <v>0.161742633</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.161745165</v>
+        <v>0.16175408</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.161740627</v>
+        <v>0.161749145</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.161747744</v>
+        <v>0.161756713</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7814,36 +7814,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.003742252</v>
+        <v>-0.003003558</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.000433648</v>
+        <v>0.0006184610000000001</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.003401123</v>
+        <v>-0.002588214</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>106.07503697</v>
+        <v>106.076200776</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.004657985</v>
+        <v>-0.008442576</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.003237208</v>
+        <v>0.008062845000000001</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.005524083</v>
+        <v>-0.012389336</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>106.066571534</v>
+        <v>106.083223329</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.006237553</v>
+        <v>-0.000505173</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.002599105</v>
+        <v>0.003121061</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7942,36 +7942,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.003742252</v>
+        <v>-0.003003558</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.000433648</v>
+        <v>0.0006184610000000001</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.003401123</v>
+        <v>-0.002588214</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>106.07503697</v>
+        <v>106.076200776</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.004657985</v>
+        <v>-0.008442576</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.003237208</v>
+        <v>0.008062845000000001</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.005524083</v>
+        <v>-0.012389336</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>106.066571534</v>
+        <v>106.083223329</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.006237553</v>
+        <v>-0.000505173</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.002599105</v>
+        <v>0.003121061</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8211,23 +8211,23 @@
         <v>0.308299187</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>-0.001963351</v>
+        <v>-0.001098542</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.049882904</v>
+        <v>-0.046797857</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.025412867</v>
+        <v>-0.022534796</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.239409191</v>
+        <v>0.238504232</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.003244567</v>
+        <v>-0.007401249</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.035253654</v>
+        <v>-0.050458622</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8339,23 +8339,23 @@
         <v>-0.388989622</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.005366839</v>
+        <v>0.003030686</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.133768762</v>
+        <v>0.125897016</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.057109622</v>
+        <v>0.051325059</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.496017606</v>
+        <v>-0.505052117</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.016531503</v>
+        <v>0.039217793</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.176127647</v>
+        <v>0.255376344</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1474441567056602</v>
+        <v>0.1474256112199129</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1604203613810716</v>
+        <v>0.1604199917688038</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03936622001636177</v>
+        <v>0.03935318323580517</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.0219677827402049</v>
+        <v>0.02196433188205646</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/092460_model.xlsx
+++ b/argus/kship/models/092460_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 167314억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167299억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 175973억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 175957억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164233억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 164217억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 169448억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 169430억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 177774억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 177772억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 167314억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167299억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 175973억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 175957억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164233억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 164217억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 169448억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 169430억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 177774억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 177772억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -5050,35 +5050,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5169,35 +5169,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5288,35 +5288,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5407,35 +5407,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5526,35 +5526,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5645,35 +5645,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5764,35 +5764,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5883,35 +5883,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6018,7 +6018,7 @@
         <v>16830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>17080</v>
+        <v>17050</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6291,7 +6291,7 @@
         <v>16620.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>16935</v>
+        <v>16966</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6459,20 +6459,20 @@
         <v>0.259566621</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.308850207</v>
+        <v>0.308720629</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.369402888</v>
+        <v>0.369272798</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.09493478299999999</v>
+        <v>0.09483335699999999</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.058134528</v>
+        <v>0.058026871</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.062503094</v>
+        <v>0.06260829399999999</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6773,20 +6773,20 @@
         <v>0.161743175</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.161752331</v>
+        <v>0.161751844</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.161742633</v>
+        <v>0.161758</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.16175408</v>
+        <v>0.161750537</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.161749145</v>
+        <v>0.161745253</v>
       </c>
       <c r="AN23" s="24" t="n">
         <v>0.161756713</v>
@@ -7814,36 +7814,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.003003558</v>
+        <v>-0.002857395</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.0006184610000000001</v>
+        <v>0.000416954</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.002588214</v>
+        <v>-0.002650096</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>106.076200776</v>
+        <v>106.075805929</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.008442576</v>
+        <v>-0.010563511</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.008062845000000001</v>
+        <v>-0.002788899</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.012389336</v>
+        <v>0.005671942</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>106.083223329</v>
+        <v>106.072899612</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.000505173</v>
+        <v>-0.002506456</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.003121061</v>
+        <v>-0.000604357</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7942,36 +7942,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.003003558</v>
+        <v>-0.002857395</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.0006184610000000001</v>
+        <v>0.000416954</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.002588214</v>
+        <v>-0.002650096</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>106.076200776</v>
+        <v>106.075805929</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.008442576</v>
+        <v>-0.010563511</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.008062845000000001</v>
+        <v>-0.002788899</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.012389336</v>
+        <v>0.005671942</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>106.083223329</v>
+        <v>106.072899612</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.000505173</v>
+        <v>-0.002506456</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.003121061</v>
+        <v>-0.000604357</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8214,20 +8214,20 @@
         <v>-0.001098542</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.046797857</v>
+        <v>-0.046774458</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.022534796</v>
+        <v>-0.022534243</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.238504232</v>
+        <v>0.238523355</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.007401249</v>
+        <v>-0.007380672</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.050458622</v>
+        <v>-0.05045553</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8342,20 +8342,20 @@
         <v>0.003030686</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.125897016</v>
+        <v>0.125834068</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.051325059</v>
+        <v>0.051327928</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.505052117</v>
+        <v>-0.5051321600000001</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.039217793</v>
+        <v>0.039118753</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.255376344</v>
+        <v>0.25545558</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9018,11 +9018,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>17080</v>
+        <v>17050</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,830원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,950원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1474256112199129</v>
+        <v>0.1474349254485722</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1604199917688038</v>
+        <v>0.1604207322459665</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03935318323580517</v>
+        <v>0.03943593210833301</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02196433188205646</v>
+        <v>0.02199909771321496</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40086,7 +40086,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.53</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="32">
@@ -40136,7 +40136,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.92</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/092460_model.xlsx
+++ b/argus/kship/models/092460_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -681,37 +681,37 @@
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 160141억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 161069억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 167299억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 169879억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 175957억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 179192억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164217억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167361억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 169430억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 170976억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 177772억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 176561억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1668,37 +1668,37 @@
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 160141억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 161069억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 167299억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 169879억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 175957억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 179192억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164217억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167361억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 169430억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 170976억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 177772억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 176561억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2040,25 +2040,25 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 179억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 181억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 188억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 191억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 93억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 98억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 97억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 102억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2100,25 +2100,25 @@
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 179억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 181억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 188억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 191억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 93억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 98억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 97억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 102억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4179,7 +4179,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4387,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 7.1, "op_wape_pct": 14.2, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 8.4, "wape_trend": 37.3, "adopted": true, "decision": "adopted"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 335.57, "rev_act": 316.68, "op_pred": 51.45, "op_act": 54.41}, {"q": "2025Q4", "rev_pred": 430.75, "rev_act": 395.91, "op_pred": 66.05, "op_act": 55.42}, {"q": "2026Q1", "rev_pred": 368.08, "rev_act": 393.57, "op_pred": 56.44, "op_act": 55.18}, {"q": "2026Q2", "rev_pred": 458.41, "rev_act": 428.36, "op_pred": 70.29, "op_act": 91.94}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 7.1, "op_wape_pct": 14.2, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": null, "wape_trend": 37.3, "adopted": "undetermined", "decision": "undetermined", "note": "현재 채택 조합(suppliers_mentions·시차 4·ma4·창 8)을 동결 데이터로 재적합할 수 없음(짝·고객 모델 부족) → 연동 WAPE 없음, undetermined(유의성 조건만으로 채택)"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 335.57, "rev_act": 316.68, "op_pred": 51.45, "op_act": 54.41}, {"q": "2025Q4", "rev_pred": 430.75, "rev_act": 395.91, "op_pred": 66.05, "op_act": 55.42}, {"q": "2026Q1", "rev_pred": 368.08, "rev_act": 393.57, "op_pred": 56.44, "op_act": 55.18}, {"q": "2026Q2", "rev_pred": 458.41, "rev_act": 428.36, "op_pred": 70.29, "op_act": 91.94}]}</t>
         </is>
       </c>
     </row>
@@ -6456,23 +6456,23 @@
         <v>0.150825435</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.259566621</v>
+        <v>0.266889052</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.308720629</v>
+        <v>0.328913269</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.369272798</v>
+        <v>0.394458176</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.09483335699999999</v>
+        <v>0.115787979</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.058026871</v>
+        <v>0.061501905</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.06260829399999999</v>
+        <v>0.039327851</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6770,26 +6770,26 @@
         <v>0.161754265</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.161743175</v>
+        <v>0.161750225</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.161751844</v>
+        <v>0.161747977</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.161758</v>
+        <v>0.161747145</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.161750537</v>
+        <v>0.161748932</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.161745253</v>
+        <v>0.161756105</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.161756713</v>
+        <v>0.161756888</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7814,36 +7814,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.002857395</v>
+        <v>-0.003303065</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.000416954</v>
+        <v>2.5209e-05</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.002650096</v>
+        <v>-0.003009558</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>106.075805929</v>
+        <v>106.075473964</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.010563511</v>
+        <v>-0.00484392</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.002788899</v>
+        <v>-0.001803216</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.005671942</v>
+        <v>6.396700000000001e-05</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>106.072899612</v>
+        <v>106.072235048</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.002506456</v>
+        <v>-0.001521883</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.000604357</v>
+        <v>-0.001967307</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7942,36 +7942,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.002857395</v>
+        <v>-0.003303065</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.000416954</v>
+        <v>2.5209e-05</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.002650096</v>
+        <v>-0.003009558</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>106.075805929</v>
+        <v>106.075473964</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.010563511</v>
+        <v>-0.00484392</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.002788899</v>
+        <v>-0.001803216</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.005671942</v>
+        <v>6.396700000000001e-05</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>106.072899612</v>
+        <v>106.072235048</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.002506456</v>
+        <v>-0.001521883</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.000604357</v>
+        <v>-0.001967307</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8211,23 +8211,23 @@
         <v>0.308299187</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>-0.001098542</v>
+        <v>-0.001963351</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.046774458</v>
+        <v>-0.049859485</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.022534243</v>
+        <v>-0.025929851</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.238523355</v>
+        <v>0.236670968</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.007380672</v>
+        <v>-0.008778032</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.05045553</v>
+        <v>-0.049852404</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8339,23 +8339,23 @@
         <v>-0.388989622</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.003030686</v>
+        <v>0.005366839</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.125834068</v>
+        <v>0.13370596</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.051327928</v>
+        <v>0.058276091</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.5051321600000001</v>
+        <v>-0.489583333</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.039118753</v>
+        <v>0.043995488</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.25545558</v>
+        <v>0.237229862</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1474349254485722</v>
+        <v>0.1474383111178051</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1604207322459665</v>
+        <v>0.1604212256557464</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03943593210833301</v>
+        <v>0.03939379876013675</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02199909771321496</v>
+        <v>0.02198050308463168</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/092460_model.xlsx
+++ b/argus/kship/models/092460_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 169879억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 169874억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 179192억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 179230억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 167361억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167439억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 170976억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 171095억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 176561억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 176725억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 169879억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 169874억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 179192억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 179230억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 167361억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167439억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 170976억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 171095억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 176561억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 176725억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -5050,35 +5050,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5169,35 +5169,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5288,35 +5288,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5407,35 +5407,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5526,35 +5526,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5645,35 +5645,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5764,35 +5764,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5883,35 +5883,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6018,7 +6018,7 @@
         <v>16830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>17050</v>
+        <v>16700</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6291,7 +6291,7 @@
         <v>16620.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>16966</v>
+        <v>16896</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6459,20 +6459,20 @@
         <v>0.266889052</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.328913269</v>
+        <v>0.328870076</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.394458176</v>
+        <v>0.394744374</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.115787979</v>
+        <v>0.116295109</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.061501905</v>
+        <v>0.062229738</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.039327851</v>
+        <v>0.040320484</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6773,23 +6773,23 @@
         <v>0.161750225</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.161747977</v>
+        <v>0.161753234</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.161747145</v>
+        <v>0.161751264</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.161748932</v>
+        <v>0.161748137</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.161756105</v>
+        <v>0.161746035</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.161756888</v>
+        <v>0.161748395</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7814,36 +7814,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.003303065</v>
+        <v>-0.003125471</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>2.5209e-05</v>
+        <v>0.000188303</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.003009558</v>
+        <v>-0.002858457</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>106.075473964</v>
+        <v>106.075619154</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.00484392</v>
+        <v>-0.004987131</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.001803216</v>
+        <v>-0.001915302</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>6.396700000000001e-05</v>
+        <v>-0.003036076</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>106.072235048</v>
+        <v>106.076386082</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.001521883</v>
+        <v>-0.00878224</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.001967307</v>
+        <v>-0.004665281</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7942,36 +7942,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.003303065</v>
+        <v>-0.003125471</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>2.5209e-05</v>
+        <v>0.000188303</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.003009558</v>
+        <v>-0.002858457</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>106.075473964</v>
+        <v>106.075619154</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.00484392</v>
+        <v>-0.004987131</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.001803216</v>
+        <v>-0.001915302</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>6.396700000000001e-05</v>
+        <v>-0.003036076</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>106.072235048</v>
+        <v>106.076386082</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.001521883</v>
+        <v>-0.00878224</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.001967307</v>
+        <v>-0.004665281</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8214,20 +8214,20 @@
         <v>-0.001963351</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.049859485</v>
+        <v>-0.049836066</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.025929851</v>
+        <v>-0.025978507</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.236670968</v>
+        <v>0.236575738</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.008778032</v>
+        <v>-0.008881249000000001</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.049852404</v>
+        <v>-0.050027874</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8342,20 +8342,20 @@
         <v>0.005366839</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.13370596</v>
+        <v>0.133643158</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.058276091</v>
+        <v>0.058390117</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.489583333</v>
+        <v>-0.489348338</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.043995488</v>
+        <v>0.044485445</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.237229862</v>
+        <v>0.237782139</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9018,11 +9018,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>17050</v>
+        <v>16700</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,950원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 17,130원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1474383111178051</v>
+        <v>0.1474371039588431</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1604212256557464</v>
+        <v>0.1604204807887903</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03939379876013675</v>
+        <v>0.03940692783286407</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02198050308463168</v>
+        <v>0.02198605299117685</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -40086,7 +40086,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="32">
@@ -40096,7 +40096,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="33">
@@ -40136,7 +40136,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/092460_model.xlsx
+++ b/argus/kship/models/092460_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 169874억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 169869억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 179230억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 179207억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 167439억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167399억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 171095억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 171038억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 176725억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 176657억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 169874억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 169869억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 179230억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 179207억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 167439억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167399억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 171095억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 171038억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 176725억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 176657억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4179,7 +4179,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5050,35 +5050,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5169,35 +5169,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5288,35 +5288,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5407,35 +5407,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5526,35 +5526,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5645,35 +5645,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5764,35 +5764,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5883,35 +5883,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6459,20 +6459,20 @@
         <v>0.266889052</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.328870076</v>
+        <v>0.328826883</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.394744374</v>
+        <v>0.394562248</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.116295109</v>
+        <v>0.116031402</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.062229738</v>
+        <v>0.061887229</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.040320484</v>
+        <v>0.039964245</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6773,23 +6773,23 @@
         <v>0.161750225</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.161753234</v>
+        <v>0.161758492</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.161751264</v>
+        <v>0.161753731</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.161748137</v>
+        <v>0.161750005</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.161746035</v>
+        <v>0.161757887</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.161748395</v>
+        <v>0.16174655</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7814,36 +7814,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.003125471</v>
+        <v>-0.002786231</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.000188303</v>
+        <v>0.0006451989999999999</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.002858457</v>
+        <v>-0.002487275</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>106.075619154</v>
+        <v>106.076120236</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.004987131</v>
+        <v>-0.004367338</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.001915302</v>
+        <v>0.008861515</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.003036076</v>
+        <v>-0.010900788</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>106.076386082</v>
+        <v>106.079912271</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.00878224</v>
+        <v>0.004653363</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.004665281</v>
+        <v>-0.008301879999999999</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7942,36 +7942,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.003125471</v>
+        <v>-0.002786231</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.000188303</v>
+        <v>0.0006451989999999999</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.002858457</v>
+        <v>-0.002487275</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>106.075619154</v>
+        <v>106.076120236</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.004987131</v>
+        <v>-0.004367338</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.001915302</v>
+        <v>0.008861515</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.003036076</v>
+        <v>-0.010900788</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>106.076386082</v>
+        <v>106.079912271</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.00878224</v>
+        <v>0.004653363</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.004665281</v>
+        <v>-0.008301879999999999</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8218,16 +8218,16 @@
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.025978507</v>
+        <v>-0.02595386</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.236575738</v>
+        <v>0.23662036</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.008881249000000001</v>
+        <v>-0.008839779000000001</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.050027874</v>
+        <v>-0.04994013</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8346,16 +8346,16 @@
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.058390117</v>
+        <v>0.058334718</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.489348338</v>
+        <v>-0.489478643</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.044485445</v>
+        <v>0.044294063</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.237782139</v>
+        <v>0.237506136</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1474371039588431</v>
+        <v>0.1474305076237686</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1604204807887903</v>
+        <v>0.1604223677806942</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03940692783286407</v>
+        <v>0.03939981621406172</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02198605299117685</v>
+        <v>0.0219829863189656</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/092460_model.xlsx
+++ b/argus/kship/models/092460_model.xlsx
@@ -4179,7 +4179,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/092460_model.xlsx
+++ b/argus/kship/models/092460_model.xlsx
@@ -4179,7 +4179,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6018,7 @@
         <v>16830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>16700</v>
+        <v>16560</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6291,7 +6291,7 @@
         <v>16620.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>16896</v>
+        <v>16840</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>16700</v>
+        <v>16560</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32813,7 +32813,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40086,7 +40086,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.25</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="32">
@@ -40096,7 +40096,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="33">
@@ -40136,7 +40136,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.7</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/092460_model.xlsx
+++ b/argus/kship/models/092460_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 169869억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 169855억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 179207억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 179120억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 167399억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167240억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 171038억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 170807억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 176657억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 176369억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 169869억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 169855억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 179207억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 179120억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 167399억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167240억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 171038억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 170807억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 176657억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 176369억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2052,7 +2052,7 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 98억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 97억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2112,7 +2112,7 @@
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 98억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 97억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4179,7 +4179,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 3.94% / 부채 2.20% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0394, 0.022] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)", "debt": "CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)"}</t>
+          <t>· 이자율 자산 3.95% / 부채 2.20% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0394, 0.022] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)", "debt": "CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)"}</t>
         </is>
       </c>
     </row>
@@ -5050,35 +5050,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5169,35 +5169,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5288,35 +5288,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5407,35 +5407,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5526,35 +5526,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5645,35 +5645,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5764,35 +5764,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5883,35 +5883,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6018,7 +6018,7 @@
         <v>16830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>16560</v>
+        <v>16330</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6200,7 +6200,7 @@
         <v>13770</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>16000</v>
+        <v>15720</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6291,7 +6291,7 @@
         <v>16620.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>16840</v>
+        <v>16782.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6459,20 +6459,20 @@
         <v>0.266889052</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.328826883</v>
+        <v>0.328718901</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.394562248</v>
+        <v>0.393885781</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.116031402</v>
+        <v>0.114976571</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.061887229</v>
+        <v>0.060452969</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.039964245</v>
+        <v>0.038342137</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6773,23 +6773,23 @@
         <v>0.161750225</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.161758492</v>
+        <v>0.161755384</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.161753731</v>
+        <v>0.161757569</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.161750005</v>
+        <v>0.161757482</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.161757887</v>
+        <v>0.161754613</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.16174655</v>
+        <v>0.16174629</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7814,36 +7814,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.002786231</v>
+        <v>-0.002418528</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.0006451989999999999</v>
+        <v>0.000830364</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.002487275</v>
+        <v>-0.002256478</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>106.076120236</v>
+        <v>106.076188604</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.004367338</v>
+        <v>-0.005543283</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.008861515</v>
+        <v>-0.0008874380000000001</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.010900788</v>
+        <v>0.003985084</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>106.079912271</v>
+        <v>106.080484136</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.004653363</v>
+        <v>-0.002082228</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.008301879999999999</v>
+        <v>-0.01695103</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7942,36 +7942,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.002786231</v>
+        <v>-0.002418528</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.0006451989999999999</v>
+        <v>0.000830364</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.002487275</v>
+        <v>-0.002256478</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>106.076120236</v>
+        <v>106.076188604</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.004367338</v>
+        <v>-0.005543283</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.008861515</v>
+        <v>-0.0008874380000000001</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.010900788</v>
+        <v>0.003985084</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>106.079912271</v>
+        <v>106.080484136</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.004653363</v>
+        <v>-0.002082228</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.008301879999999999</v>
+        <v>-0.01695103</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8214,20 +8214,20 @@
         <v>-0.001963351</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.049836066</v>
+        <v>-0.049812646</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.02595386</v>
+        <v>-0.025854632</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.23662036</v>
+        <v>0.236767534</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.008839779000000001</v>
+        <v>-0.008653492</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.04994013</v>
+        <v>-0.049608948</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8342,20 +8342,20 @@
         <v>0.005366839</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.133643158</v>
+        <v>0.133580355</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.058334718</v>
+        <v>0.058116343</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.489478643</v>
+        <v>-0.489973297</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.044294063</v>
+        <v>0.0434247</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.237506136</v>
+        <v>0.236521055</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9018,11 +9018,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>16560</v>
+        <v>16330</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 17,130원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 17,050원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1474305076237686</v>
+        <v>0.1474329194028351</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1604223677806942</v>
+        <v>0.1604201880229651</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03939981621406172</v>
+        <v>0.03945829579762793</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.0219829863189656</v>
+        <v>0.02200740653988508</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32813,7 +32813,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40086,7 +40086,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.14</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="32">
@@ -40096,7 +40096,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="33">
@@ -40136,7 +40136,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.62</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/092460_model.xlsx
+++ b/argus/kship/models/092460_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 169855억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 169852억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 179120억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 179190억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 167240억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167382억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 170807억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 171021억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 176369억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 176656억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 169855억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 169852억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 179120억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 179190억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 167240억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167382억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 170807억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 171021억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 176369억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 176656억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2052,7 +2052,7 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 97억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 98억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2112,7 +2112,7 @@
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 97억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 98억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4179,7 +4179,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 3.95% / 부채 2.20% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0394, 0.022] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)", "debt": "CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)"}</t>
+          <t>· 이자율 자산 3.94% / 부채 2.20% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0394, 0.022] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)", "debt": "CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)"}</t>
         </is>
       </c>
     </row>
@@ -5050,35 +5050,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5169,35 +5169,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5288,35 +5288,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5407,35 +5407,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5526,35 +5526,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5645,35 +5645,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5764,35 +5764,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5883,35 +5883,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6018,7 +6018,7 @@
         <v>16830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>16330</v>
+        <v>16750</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6109,7 +6109,7 @@
         <v>19040</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>17180</v>
+        <v>17200</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6291,7 +6291,7 @@
         <v>16620.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>16782.9</v>
+        <v>16782.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6459,20 +6459,20 @@
         <v>0.266889052</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.328718901</v>
+        <v>0.328697305</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.393885781</v>
+        <v>0.394432158</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.114976571</v>
+        <v>0.115929975</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.060452969</v>
+        <v>0.061780194</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.038342137</v>
+        <v>0.040049412</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6773,23 +6773,23 @@
         <v>0.161750225</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.161755384</v>
+        <v>0.161758013</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.161757569</v>
+        <v>0.161750163</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.161757482</v>
+        <v>0.161746528</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.161754613</v>
+        <v>0.161754032</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.16174629</v>
+        <v>0.161749078</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7814,36 +7814,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.002418528</v>
+        <v>-0.003246024</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.000830364</v>
+        <v>8.7204e-05</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.002256478</v>
+        <v>-0.002952565</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>106.076188604</v>
+        <v>106.075537049</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.005543283</v>
+        <v>-0.004792741</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.0008874380000000001</v>
+        <v>-0.000268132</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.003985084</v>
+        <v>-4.6042e-05</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>106.080484136</v>
+        <v>106.07065254</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.002082228</v>
+        <v>0.005492332</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.01695103</v>
+        <v>-0.009114651</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7942,36 +7942,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.002418528</v>
+        <v>-0.003246024</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.000830364</v>
+        <v>8.7204e-05</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.002256478</v>
+        <v>-0.002952565</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>106.076188604</v>
+        <v>106.075537049</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.005543283</v>
+        <v>-0.004792741</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.0008874380000000001</v>
+        <v>-0.000268132</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.003985084</v>
+        <v>-4.6042e-05</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>106.080484136</v>
+        <v>106.07065254</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.002082228</v>
+        <v>0.005492332</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.01695103</v>
+        <v>-0.009114651</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8218,16 +8218,16 @@
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.025854632</v>
+        <v>-0.025928573</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.236767534</v>
+        <v>0.236633688</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.008653492</v>
+        <v>-0.008839236</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.049608948</v>
+        <v>-0.049937037</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8346,16 +8346,16 @@
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.058116343</v>
+        <v>0.058282548</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.489973297</v>
+        <v>-0.489582243</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.0434247</v>
+        <v>0.044307692</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.236521055</v>
+        <v>0.237576115</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9018,11 +9018,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>16330</v>
+        <v>16750</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 17,050원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,680원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1474329194028351</v>
+        <v>0.1474379086607849</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1604201880229651</v>
+        <v>0.160421428884873</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03945829579762793</v>
+        <v>0.03939425591460759</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02200740653988508</v>
+        <v>0.02198045331953434</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32813,7 +32813,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40086,7 +40086,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.98</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="32">
@@ -40096,7 +40096,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="33">
@@ -40136,7 +40136,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.48</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/092460_model.xlsx
+++ b/argus/kship/models/092460_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 169852억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 169840억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 179190억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 179097억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 167382억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167209억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 171021억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 170767억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 176656억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 176335억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 169852억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 169840억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 179190억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 179097억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 167382억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167209억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 171021억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 170767억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 176656억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 176335억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2040,7 +2040,7 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 181억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 180억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2052,7 +2052,7 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 98억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 97억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2100,7 +2100,7 @@
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 181억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 180억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2112,7 +2112,7 @@
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 98억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 97억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4179,7 +4179,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 3.94% / 부채 2.20% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0394, 0.022] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)", "debt": "CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)"}</t>
+          <t>· 이자율 자산 3.95% / 부채 2.20% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0394, 0.022] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)", "debt": "CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)"}</t>
         </is>
       </c>
     </row>
@@ -5050,35 +5050,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5169,35 +5169,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5288,35 +5288,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5407,35 +5407,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5526,35 +5526,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5645,35 +5645,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5764,35 +5764,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5883,35 +5883,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6018,7 +6018,7 @@
         <v>16830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>16750</v>
+        <v>16090</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6200,7 +6200,7 @@
         <v>13770</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>15720</v>
+        <v>15710</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6291,7 +6291,7 @@
         <v>16620.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>16782.5</v>
+        <v>16562.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6459,20 +6459,20 @@
         <v>0.266889052</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.328697305</v>
+        <v>0.328610919</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.394432158</v>
+        <v>0.393703656</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.115929975</v>
+        <v>0.114773718</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.061780194</v>
+        <v>0.060196087</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.040049412</v>
+        <v>0.038231469</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6773,23 +6773,23 @@
         <v>0.161750225</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.161758013</v>
+        <v>0.161752276</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.161750163</v>
+        <v>0.161760039</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.161746528</v>
+        <v>0.161750523</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.161754032</v>
+        <v>0.161753422</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.161749078</v>
+        <v>0.161745366</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7814,36 +7814,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.003246024</v>
+        <v>-0.003233775</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>8.7204e-05</v>
+        <v>-0.000163406</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.002952565</v>
+        <v>-0.003087248</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>106.075537049</v>
+        <v>106.075145985</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.004792741</v>
+        <v>-0.00636617</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.000268132</v>
+        <v>-0.0005476050000000001</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-4.6042e-05</v>
+        <v>-0.005543415</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>106.07065254</v>
+        <v>106.08229941</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.005492332</v>
+        <v>-0.010167895</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.009114651</v>
+        <v>-0.00551192</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7942,36 +7942,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.003246024</v>
+        <v>-0.003233775</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>8.7204e-05</v>
+        <v>-0.000163406</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.002952565</v>
+        <v>-0.003087248</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>106.075537049</v>
+        <v>106.075145985</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.004792741</v>
+        <v>-0.00636617</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.000268132</v>
+        <v>-0.0005476050000000001</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-4.6042e-05</v>
+        <v>-0.005543415</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>106.07065254</v>
+        <v>106.08229941</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.005492332</v>
+        <v>-0.010167895</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.009114651</v>
+        <v>-0.00551192</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8218,16 +8218,16 @@
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.025928573</v>
+        <v>-0.025829985</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.236633688</v>
+        <v>0.236812144</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.008839236</v>
+        <v>-0.008612049</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.049937037</v>
+        <v>-0.049583196</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8346,16 +8346,16 @@
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.058282548</v>
+        <v>0.058060942</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.489582243</v>
+        <v>-0.490103676</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.044307692</v>
+        <v>0.043232697</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.237576115</v>
+        <v>0.236539029</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9018,11 +9018,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>16750</v>
+        <v>16090</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,680원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 15,780원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1474379086607849</v>
+        <v>0.1474458787483048</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.160421428884873</v>
+        <v>0.1604189493137589</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03939425591460759</v>
+        <v>0.03945119172069379</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02198045331953434</v>
+        <v>0.02200434224874231</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32813,7 +32813,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40086,7 +40086,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.28</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="32">
@@ -40096,7 +40096,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="33">
@@ -40136,7 +40136,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.73</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/092460_model.xlsx
+++ b/argus/kship/models/092460_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 169840억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 169797억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 179097억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 178987억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 167209억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167034억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 170767억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 170527억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 176335억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 176072억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 169840억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 169797억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 179097억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 178987억 × 비례계수 0.0128 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 167209억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167034억 × 비례계수 0.0128 × 계절비중 Q2 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 170767억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 170527억 × 비례계수 0.0128 × 계절비중 Q3 0.227(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 176335억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 176072억 × 비례계수 0.0128 × 계절비중 Q4 0.283(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=1.00, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2058,7 +2058,7 @@
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 102억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 101억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2118,7 +2118,7 @@
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 102억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 101억 × 3.94%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 571억 × 2.20%(CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4179,7 +4179,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4307,7 +4307,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 14.74% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 14.74% · 근거: 최근 12분기 유효세율 14.7%(5~27% 안 — 그대로)</t>
+          <t>· 세율 14.75% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 14.74% · 근거: 최근 12분기 유효세율 14.7%(5~27% 안 — 그대로)</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 3.95% / 부채 2.20% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0394, 0.022] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)", "debt": "CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)"}</t>
+          <t>· 이자율 자산 3.94% / 부채 2.20% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0394, 0.022] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)", "debt": "CF 이자지급 ÷ 평균 총차입금(2026Q1~2026Q2; 주석 이자비용 0분기 &lt; 4)"}</t>
         </is>
       </c>
     </row>
@@ -5050,35 +5050,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5169,35 +5169,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5288,35 +5288,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5407,35 +5407,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5526,35 +5526,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5645,35 +5645,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5764,35 +5764,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5883,35 +5883,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6018,7 +6018,7 @@
         <v>16830</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>16090</v>
+        <v>13700</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6200,7 +6200,7 @@
         <v>13770</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>15710</v>
+        <v>13490</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6291,7 +6291,7 @@
         <v>16620.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>16562.7</v>
+        <v>15941.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6459,20 +6459,20 @@
         <v>0.266889052</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.328610919</v>
+        <v>0.328265377</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.393703656</v>
+        <v>0.392871081</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.114773718</v>
+        <v>0.113597176</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.060196087</v>
+        <v>0.058719014</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.038231469</v>
+        <v>0.036956946</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6773,23 +6773,23 @@
         <v>0.161750225</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.161752276</v>
+        <v>0.161745578</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.161760039</v>
+        <v>0.161744653</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.161750523</v>
+        <v>0.161757473</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.161753422</v>
+        <v>0.161756678</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.161745366</v>
+        <v>0.161751101</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7814,36 +7814,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.003233775</v>
+        <v>-0.00381243</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.000163406</v>
+        <v>-0.000747376</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.003087248</v>
+        <v>-0.003602259</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>106.075145985</v>
+        <v>106.074595967</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.00636617</v>
+        <v>-0.006131614</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.0005476050000000001</v>
+        <v>-0.0060425</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.005543415</v>
+        <v>-0.006864322</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>106.08229941</v>
+        <v>106.074889568</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.010167895</v>
+        <v>0.005457915</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.00551192</v>
+        <v>-0.00491869</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7942,36 +7942,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.003233775</v>
+        <v>-0.00381243</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>-0.000163406</v>
+        <v>-0.000747376</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.003087248</v>
+        <v>-0.003602259</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>106.075145985</v>
+        <v>106.074595967</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.00636617</v>
+        <v>-0.006131614</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.0005476050000000001</v>
+        <v>-0.0060425</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.005543415</v>
+        <v>-0.006864322</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>106.08229941</v>
+        <v>106.074889568</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.010167895</v>
+        <v>0.005457915</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.00551192</v>
+        <v>-0.00491869</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8214,20 +8214,20 @@
         <v>-0.001963351</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.049812646</v>
+        <v>-0.049765808</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.025829985</v>
+        <v>-0.025705484</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.236812144</v>
+        <v>0.236972579</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.008612049</v>
+        <v>-0.008425358000000001</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.049583196</v>
+        <v>-0.049269922</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8342,20 +8342,20 @@
         <v>0.005366839</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.133580355</v>
+        <v>0.133454751</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.058060942</v>
+        <v>0.057790337</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.490103676</v>
+        <v>-0.490702425</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.043232697</v>
+        <v>0.042373753</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.236539029</v>
+        <v>0.23571781</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9018,11 +9018,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>16090</v>
+        <v>13700</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 15,780원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,620원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1474458787483048</v>
+        <v>0.1474520052266559</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1604189493137589</v>
+        <v>0.160421571387779</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03945119172069379</v>
+        <v>0.03941615912074852</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02200434224874231</v>
+        <v>0.02198898473053751</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32813,7 +32813,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40086,7 +40086,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="32">
@@ -40096,7 +40096,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="33">
@@ -40136,7 +40136,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.34</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="37">
